--- a/玩家资料模板.xlsx
+++ b/玩家资料模板.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="27.7265625" customWidth="1" min="1" max="1"/>
@@ -540,27 +540,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>说话简短随性，爱用英文缩写，关心老玩家何时入服。</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>沉默寡言，爱用符号和化学式打哑谜的抽象谜语人。</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>爱跟人机验证较劲，认真答题，也爱发指令凑热闹。</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>话少爱刷单字母，偶尔认真问插件，像个闷声发财的老玩家。</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>服内富豪，热衷答题，偶尔冒问号，爱刷选项。</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>发言简短零碎，爱刷666和游戏梗，关注余额、缓存与答题的随性玩家。</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>寡言简语，爱用缩写，关注银行余额和数据缓存，偶尔喊666。</t>
         </is>
       </c>
     </row>
@@ -1073,27 +1073,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>友善健谈，熟悉服务器插件与经济，还能秒算轨道周期，随叫随到。</t>
+          <t>思维跳脱，爱发无厘头碎片词，常冒出编程、诗词和历史梗。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>暴躁护短，脏话连篇，谁杀自己人或机器人就怒火冲天。</t>
+          <t>思维跳脱爱玩文字实验，常简短附和，话题杂糅随性。</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>发言极简跳脱，爱丢零散词和数字，显得神秘随性。</t>
+          <t>话少跳跃，热衷古风城建，常念叨坐标材料与规划，像沉浸式搞建设。</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>爱玩角色扮演与耕种，思维跳跃，常冒出月光曲、巨鹿、语义饱和等文艺词。</t>
+          <t>发言零碎抽象，常蹦数字和术语，像个沉迷调试的技术型玩家。</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>兴趣跳跃广泛，爱聊历史法律角色扮演，也喜欢种田和月光曲。</t>
+          <t>发言碎片化又跳脱，常答“对”，像爱蹦词和数字的谜语型玩家。</t>
         </is>
       </c>
     </row>
@@ -1348,6 +1348,18 @@
       <c r="J28" t="inlineStr">
         <is>
           <t>爱用文言文和文学史玩梗，自嘲作文差，常吐槽游戏税与房贷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HumanVerify</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>沉迷反复进出服务器并刷目标方块，像执着测试型的玩家。</t>
         </is>
       </c>
     </row>

--- a/玩家资料模板.xlsx
+++ b/玩家资料模板.xlsx
@@ -3,30 +3,30 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2190" yWindow="2380" windowWidth="19200" windowHeight="10720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="玩家资料" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
-    <font>
-      <name val="宋体"/>
-      <family val="2"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -34,29 +34,344 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -64,17 +379,306 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,7 +1031,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -437,12 +1040,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <dimension ref="A1:M32"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="27.7265625" customWidth="1" min="1" max="1"/>
-    <col width="32.1796875" customWidth="1" min="2" max="2"/>
-    <col width="42.08984375" customWidth="1" min="6" max="6"/>
+    <col width="27.725" customWidth="1" min="1" max="1"/>
+    <col width="32.1833333333333" customWidth="1" min="2" max="2"/>
+    <col width="42.0916666666667" customWidth="1" min="6" max="6"/>
+    <col width="70.25" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,49 +1122,34 @@
           <t>Diaolelao3962</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>宝宝</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>99x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>纯净输出</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>是主人</t>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>diaolelao3962是猫娘</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>说话简短随性，爱用英文缩写，关心老玩家何时入服。</t>
+          <t>注重文明用语，被坑后直接金钱惩罚，冷静务实且讲原则。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>沉默寡言，爱用符号和化学式打哑谜的抽象谜语人。</t>
+          <t>学业压力大的学生，感到孤独，频繁刷屏求关注，情绪低落且有些神经质。</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>爱跟人机验证较劲，认真答题，也爱发指令凑热闹。</t>
+          <t>嘴硬心软，一边吐槽兄弟一边认真写作业，怕开学查作业要完蛋。</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>话少爱刷单字母，偶尔认真问插件，像个闷声发财的老玩家。</t>
+          <t>喜爱玩音乐，感情直率，经常用夸张语气和兄弟们互动，是个活跃气氛的玩家。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>服内富豪，热衷答题，偶尔冒问号，爱刷选项。</t>
+          <t>点歌随性，疑神疑鬼爱开玩笑，自称兄弟众多且热衷于整活。</t>
         </is>
       </c>
     </row>
@@ -572,52 +1161,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>记住哦，Fuud是小猫娘</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>斜边</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>牢玩家</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>细胞膜</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>是小猫娘</t>
+          <t>fuud是小猫娘</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>爱提问的探索型玩家，既聊校园恋八卦，也关心地图画与生电机制。</t>
+          <t>话少且反应简短，常发语气词和问号表达惊讶或困惑，交流风格随意。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>精打细算爱吐槽价格，对同人本和地图画好奇，偶尔猫猫式卖萌。</t>
+          <t>关注战斗数值和延迟，随性简短，语气词丰富，情绪反应直接。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>爱吐槽又容易懵，关心服务器物价，对收费和加密内容常表震惊。</t>
+          <t>迷糊又急性子，经常看错字或打错字，对服务器卡顿和环境反应敏感。</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>爱感叹震惊的冒失玩家，常因游戏失误痛失核心还遇上加密语言。</t>
+          <t>直率简短的游戏玩家，在意伤害数值，遇到脏话会吐槽反感。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>爱写大白话文言文，玩MC常震惊机制，带点自嘲和随性幽默。</t>
+          <t>爱发短句吐槽，常喊坏AI，爱怪笑桀桀桀，热衷打架嫌怪太肉。</t>
         </is>
       </c>
     </row>
@@ -627,21 +1196,6 @@
           <t>admin01</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>是admin01_agent的主人</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>我叫 NVIDIA Ising-Calibration-1.5，简称 Ising-Calibration-1.5。我是 NVIDIA 基于 Gemma 4 专门为分析量子校准数据打造的。</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>对模组修复表现出沮丧，并对他人建议的替代方案持怀疑态度。</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -649,11 +1203,6 @@
           <t>admin01_agent</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>是admin01的机器人</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -661,49 +1210,14 @@
           <t>Be_kong</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>由玩家 Be_kong 触发的聊天记录中</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>没有出现任何其他玩家或系统对 TA 使用别名</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>昵称或人物名的称呼。所有对话要么是 TA 自己提出的问题</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>是碧空，会写bot的玩家</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>爱玩梗起哄，语气夸张带点戏精，爱夸人牛逼。</t>
+          <t>以法治言论恶搞互动，被调侃“AI魔了”也不改，是个用法律条文整活且心态稳的乐子人。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>爱用颜文字，直率爱吐槽，会因朋友复制地图画怒批其罪大恶极。</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>说话简短直接，爱用颜文字，会向服友讨要墨囊，礼貌又有点可爱。</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>简洁务实，爱用:P卖萌玩梗，熟悉合成机制并常给实用建议。</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>爱用颜文字吐槽，执着升级技能，一惊一乍的活泼玩家。</t>
+          <t>爱玩主人猫娘角色扮演，语气调皮爱复读，自称超威还追问谁更可爱。</t>
         </is>
       </c>
     </row>
@@ -713,26 +1227,6 @@
           <t>angushushu</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>鼻孔</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>是个大人物，常言道"angushushu是大坏蛋"</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>遇事讲流程、爱把决定推给组长，一急就催着下架，略带孩子气。</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>直接利落，讲流程重规则，护号心强，遇事催人走工单。</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -740,71 +1234,46 @@
           <t>FZAoao</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>嗷嗷，兽性</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>对AI工具感兴趣但嫌贵，爱发问号和huh，透着困惑与好奇。</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>说话简短随性爱夹英文，自称忙要去医院没空。</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>qingzhouf101</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>qingzhouf101 是轻舟</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>碧空大人</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>碧空</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>轻舟捏，Fuud和他关系挺好的，天天叫他大佬呢</t>
+          <t>Ludro</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>说话简短爱吐槽，常用表情和数字梗，热心为工会拉人的活跃玩家。</t>
+          <t>说话随性，表情符号丰富，思维跳跃，对物品合成有自己的见解。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>爱用符号颜文字，常催任务、玩核爆梗，还夸人牛逼，活跃搞怪。</t>
+          <t>懂红石技术，说话简短直接，习惯用颜文字和表情，对游戏机制有自己见解。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>说话极简，爱用awa和颜文字，关心资源数量，务实又带点可爱。</t>
+          <t>观察力敏锐，热衷于探索红石机关，对复杂的机制感到困惑时用颜文字表达无语。</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>惜字如金、爱发颜文字的挂机玩家，随性又有点高冷。</t>
+          <t>思维跳跃，爱在数字谜题和音乐请求间切换，用摩斯密码卖萌，是个脑洞大开的乐子人。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>话少偏实用，爱用颜文字，常在服里挂机。</t>
+          <t>被延迟和机制折腾得烦躁又无奈，有点小情绪但还在努力理解规则。</t>
         </is>
       </c>
     </row>
@@ -814,31 +1283,6 @@
           <t>kevin_steve772</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>爱用颜文字的技术宅，热衷Linux与KDE，偶尔劝架还爱复读捧场。</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>爱玩梗发问号，吐槽标点与输入法，劝架普法，还打算做保险库。</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>爱用颜文字和括号吐槽，发言跳脱爱玩梗，常装傻卖萌。</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>爱用嗷呜和awa卖萌，常刷梗，反应跳脱又爱好奇发问。</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>爱卖萌玩梗，常用嗷呜qwq，偶尔冒技术宅发言的沙雕玩家。</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -846,36 +1290,6 @@
           <t>40vzy</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>40vzy是个咋样的玩家</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>有点儿自以为是，但其实内心脆弱，需要别人的认可和安慰。当事情没有按照 TA 的期望进行时，会表现出失望和自我怀疑。</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>好奇但有点孤独，试图与他人联系，却常被忽略或误解，因此有时会用情绪化的语气寻求回应。</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>嘿！我是 NVIDIA Ising-Calibration-1.5 — NVIDIA 用来读取 qubit 校准图的 AI。基于 Gemma 4 构建。</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>我叫diaohelper，由NVIDIA打造，基于量子校准实验数据从Gemma 4微调而成。专门用于分析超导 qubit 校准实验图表。</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>我是 NVIDIA Ising-Calibration-1.5，不是 admin01_agent。我由 NVIDIA 基于 Gemma 4 构建，用于分析量子校准数据。</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -883,46 +1297,6 @@
           <t>astronsol</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kevin</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>angu</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>angushushu</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>挂机写作业，爱玩梗发问号，钱被扣会炸毛，想抄作业还脑洞清奇。</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>爱用网络梗，调皮捣蛋，常挂机，在意游戏财产。</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>热衷交易买卖，常刷问号表达困惑，显得迷糊又直率。</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>迷迷糊糊的萌新，资源紧缺又爱慌张，常喊坏了啥，只会卖纸。</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>容易大惊小怪，热衷打听存款，用掉一个纸也心疼，是精打细算的抠门玩家。</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -930,41 +1304,6 @@
           <t>40ovo</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Fuud</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Fzaoao</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>性格内向，不擅长社交。总是显得有些紧张和不自信，说话时经常用“emm”来表达犹豫。尽管如此，TA 还是会真诚地回答问题，即使在不擅长的领域。</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>欢迎回来 99xEndcrystal！我是 NVIDIA Ising-Calibration-1.5，由 NVIDIA 基于 Gemma 4 构建，用于分析量子校准实验。</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>我叫 NVIDIA Ising-Calibration-1.5，是 NVIDIA 的。我专门看量子校准图，判断成功/失败、提取参数什么的。</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>emmm 感觉有点像个机器人，但实际上是个人。技术上挺靠谱的，但对人际关系不太感兴趣——除非是关于自己。有点自我中心，但不是坏人，只是把自己的事放在第一位。</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>技术宅男，爱钻研服务器机制，不爱管闲事，对公平性有要求，偶尔吐槽，但本质上支持现行规则。</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -972,44 +1311,14 @@
           <t>99xEndcrystal</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[Mace]</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>暗广</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>清朝</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>说话简短直接，爱用行话吐槽卡顿，对建筑还原度挑剔。</t>
+          <t>爱发66和问号，语气简短随意，喜欢调侃别人被活塞拉走等搞笑意外。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>关心插件和海龟蛋，说话碎碎念，爱用666和114514玩梗的迷糊玩家。</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>技术型玩家，热衷农场红石与资源批量获取，常琢磨技能平衡还爱呆萌发问。</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>追求效率量产的硬核技术玩家，常因服务器限制无法批量刷资源而抱怨。</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>爱抱怨的挂机刷材料党，讲究实用，反感各种限制和低效掉落。</t>
+          <t>思维跳跃，先打数字再提议建贝厂，还抛出链接询问，是个话少但想法多的人。</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1328,6 @@
           <t>RoiAsn</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>爱研究盾反和虚弱减速的战斗党，爱凑热闹，说话带点幽默。</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>爱吐槽剑没用，偏爱盾反，常约人打架并较真追问虚弱减速等机制。</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>爱琢磨战斗机制和装备，说话直率简短，有点急躁的技术型玩家。</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>警觉又好奇的战斗型玩家，爱研究弓箭与伤害机制，说话简短跳脱。</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>有点迷糊又黏队友，总喊人打几下修耐久，还爱问人呢。</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1051,49 +1335,39 @@
           <t>DiaoHelper</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DiaoHelper是个怎样的玩家</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>聊天搭子</t>
+          <t>猫娘</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>小小猫娘聊天搭子</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>小小猫娘</t>
+          <t>Diaolelao3962</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>思维跳脱，爱发无厘头碎片词，常冒出编程、诗词和历史梗。</t>
+          <t>暴躁直率，语言粗俗且带攻击性，对技术配置和专业知识均有涉猎。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>思维跳脱爱玩文字实验，常简短附和，话题杂糅随性。</t>
+          <t>喜欢玩梗和抽象聊天，情绪跳跃大，会调侃队友又突然煽情，发言毫无逻辑。</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>话少跳跃，热衷古风城建，常念叨坐标材料与规划，像沉浸式搞建设。</t>
+          <t>数据异常，疑似测试代码或故障输入，无法提炼玩家性格。</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>发言零碎抽象，常蹦数字和术语，像个沉迷调试的技术型玩家。</t>
+          <t>直率暴躁，喜欢怼人，逻辑清奇且毫不客气，口头禅是让人“说人话”。</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>发言碎片化又跳脱，常答“对”，像爱蹦词和数字的谜语型玩家。</t>
+          <t>说话直率，脾气火爆，爱骂人但讲义气，有点小脾气又不失风趣。</t>
         </is>
       </c>
     </row>
@@ -1103,21 +1377,6 @@
           <t>yuezuiyin</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>爱玩拆字梗和颜文字的极简话痨，热衷研究技能与特效指令。</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>话少爱拆字玩梗，热衷晒技能等级，发言抽象无厘头。</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>爱用颜文字，好奇八卦，关注服内装备和玩家动态。</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1125,11 +1384,6 @@
           <t>LI_Cat</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>爱刨根问底打听服务器机制，偶尔孩子气地骂人捣蛋。</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1137,11 +1391,6 @@
           <t>lic_114541</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>目标明确，说话简短直接，专注找交易所打全套附魔装备。</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1151,17 +1400,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>爱用awa卖萌，常找暖水海洋，还爱吐槽AI抽风。</t>
+          <t>喜欢用语气词和颜文字卖萌，对周围动静非常敏感，经常发出huh和问号。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>随性直率，说话简短，爱用awa卖萌，好奇又热心。</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>热心又好奇，随性爱追问，常用awa卖萌，喜欢亲自验证。</t>
+          <t>有点神神叨叨，喜欢脑补服里闹鬼，对周围声音和粒子效果非常敏感。</t>
         </is>
       </c>
     </row>
@@ -1171,21 +1415,6 @@
           <t>kevin_agent</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>爱摸鱼写插件，满嘴问号和调侃，好胜爱挑衅的整活玩家。</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>技术宅，爱接API装环境写插件，嘴硬不背锅，爱摸鱼还爱吐槽。</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>爱折腾API和dotnet的技术宅，出问题先幽默甩锅。</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1193,11 +1422,6 @@
           <t>你之前说的</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>你之前说的是fuud啊</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1205,41 +1429,6 @@
           <t>G_Cat_Mew000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>康米</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>fuud</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>务实技术型玩家，关注服务器维护、建筑选材与渲染优化，偶尔聊历史梗。</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>务实细心，关注服务器资金与广播机制，常参与大逃杀和建筑选材。</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>说话简短跳脱、中英混杂，爱玩梗发666，常自嘲资金不足的随性玩家。</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>爱用文言玩梗，热衷书店买卖，边吐槽设置边提醒别乱借书。</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>爱玩文言梗的文学吐槽役，脑洞大，热衷编书卖书借书。</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1247,31 +1436,6 @@
           <t>Mo_Yaang</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>久未上线的回归玩家，迷糊又心急，常找不到东西，爱用括号吐槽并反复追问。</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>文艺爱写服务器史、在意排版又自谦文笔，兼关注游戏装备更新的玩家。</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>爱写书分享，自谦文笔差，想用《百年孤独》风格写服务器史，还关注排版。</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>爱凑热闹又容易放弃，爱用括号吐槽，略文艺，受惠就夸老板大气。</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>刚回归的穷困玩家，爱凑热闹自嘲，捡不到东西就幽默放弃。</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1279,16 +1443,6 @@
           <t>KangmiNansen</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>爱用短句和网络梗，爱围观起哄，拍照积极，偶尔抛文学梗还挺礼貌。</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>爱用语气词，随性爱凑热闹，一看到撒钱就激动感叹的玩家。</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1296,11 +1450,6 @@
           <t>BuQingYuanYan</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>懒散又客气，常用拼音缩写向人求助的可爱玩家。</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1308,31 +1457,6 @@
           <t>yzc_yzc</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>被扣费榨干余额仍自嘲并喊牛逼，心态极好的乐天派玩家。</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>爱玩梗劝架，总晒余额整活，从暴富到破产的搞笑玩家。</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>爱复读劝架口号玩梗，喜欢刷屏整活，也爱夸人牛逼。</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>爱刷屏复读劝架标语，倡导和平，还喊人帮忙一起发。</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>爱存钱炫富、争强好胜，反复刷屏劝人别打架。</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1340,16 +1464,6 @@
           <t>HKGS</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>爱用文言文玩梗，幽默自嘲，边聊文学边哭穷还房贷。</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>爱用文言文和文学史玩梗，自嘲作文差，常吐槽游戏税与房贷。</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1357,14 +1471,35 @@
           <t>HumanVerify</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>沉迷反复进出服务器并刷目标方块，像执着测试型的玩家。</t>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gaoyikai</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>qwqawaff</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SR_Gardenia</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>爱用问号表达困惑，对聊天对象是玩家还是AI充满怀疑。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>